--- a/TestTable_测试表.xlsx
+++ b/TestTable_测试表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\Project_Chaos\Assets\Excel\Chaos_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60AF8E0C-0F56-466C-B0EC-D9E31897B810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642B0134-4DDE-48D0-97BC-18887325DFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="TestSheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>TestTable</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -129,6 +128,10 @@
   </si>
   <si>
     <t>类名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>client</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -167,7 +170,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,6 +192,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -220,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -242,6 +251,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -523,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -569,69 +581,80 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="7" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C11" s="5">
         <v>3</v>
       </c>
     </row>

--- a/TestTable_测试表.xlsx
+++ b/TestTable_测试表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\Project_Chaos\Assets\Excel\Chaos_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642B0134-4DDE-48D0-97BC-18887325DFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7D98BD-59CE-4C24-BA90-870F577189C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>TestTable</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,6 +132,34 @@
   </si>
   <si>
     <t>client</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>head_icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>both</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>server</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -139,6 +167,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -229,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -253,6 +284,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -535,15 +572,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
@@ -551,7 +589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
@@ -559,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -569,8 +607,14 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -580,8 +624,14 @@
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -591,8 +641,14 @@
       <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -602,8 +658,14 @@
       <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>1</v>
       </c>
@@ -613,8 +675,14 @@
       <c r="C7" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -624,8 +692,14 @@
       <c r="C8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5">
+        <v>20001</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -635,8 +709,14 @@
       <c r="C9" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>20002</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>3</v>
       </c>
@@ -646,8 +726,14 @@
       <c r="C10" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5">
+        <v>20003</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>4</v>
       </c>
@@ -656,6 +742,12 @@
       </c>
       <c r="C11" s="5">
         <v>3</v>
+      </c>
+      <c r="D11" s="5">
+        <v>20004</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/TestTable_测试表.xlsx
+++ b/TestTable_测试表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\Project_Chaos\Assets\Excel\Chaos_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7D98BD-59CE-4C24-BA90-870F577189C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167D9D4B-3152-464F-849C-ACE34A2676B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>TestTable</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,10 +89,6 @@
   </si>
   <si>
     <t>CharName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英雄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -260,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -287,9 +283,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -583,7 +576,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -591,7 +584,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -605,13 +598,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -622,30 +615,30 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -653,7 +646,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -662,38 +655,38 @@
         <v>4</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>0</v>
       </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
+      <c r="D7" s="5">
+        <v>20001</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
       <c r="D8" s="5">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="E8" s="9">
         <v>1</v>
@@ -701,16 +694,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
       <c r="D9" s="5">
-        <v>20002</v>
+        <v>20003</v>
       </c>
       <c r="E9" s="9">
         <v>1</v>
@@ -718,35 +711,18 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2</v>
-      </c>
       <c r="D10" s="5">
-        <v>20003</v>
+        <v>20004</v>
       </c>
       <c r="E10" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3</v>
-      </c>
-      <c r="D11" s="5">
-        <v>20004</v>
-      </c>
-      <c r="E11" s="9">
         <v>1</v>
       </c>
     </row>
